--- a/tests/fixtures/manual_spill_cache/copy_anchor.xlsx
+++ b/tests/fixtures/manual_spill_cache/copy_anchor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\manual_spill_cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EBE9690-F64D-4B6E-844F-559719FC917C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3E42BD6-2527-4251-8B0A-7331B637D882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{C4CF8BE8-3EDC-4496-9251-C97E2D942CE6}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{FB7781DE-ABBD-4345-A11F-BE5C586C54D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D40EB2-2251-49F7-A1A0-CA54AFFF834B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9D2B71-2D3B-4B17-BDC8-1B11787E44EC}">
   <dimension ref="B2:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -466,7 +466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F4A7A5-ED34-47DD-A060-BE1D39773D3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8CF81A-6234-46D5-9D75-6118B0D8CC7D}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
